--- a/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_2406989/10.15485_2406989_soil_Carbon__Dissolved_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_2406989/10.15485_2406989_soil_Carbon__Dissolved_organic_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -22466,12 +22466,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>CT-EBRA:2</t>
+          <t>CT-EBRA:2019-08-05</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr"/>
@@ -22524,12 +22524,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>CT-MOOS:4</t>
+          <t>CT-MOOS:2019-08-05</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr"/>
@@ -22582,12 +22582,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>CT-SLPR:9</t>
+          <t>CT-SLPR:2019-08-05</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr"/>
@@ -22640,12 +22640,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>CT-PASS:6</t>
+          <t>CT-PASS:2019-08-06</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr"/>
@@ -22698,12 +22698,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>CT-POPE:8</t>
+          <t>CT-POPE:2019-08-06</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr"/>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>CT-W9:13</t>
+          <t>CT-W9:2019-08-06</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr"/>
@@ -22814,12 +22814,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>EAS-BRA:25</t>
+          <t>EAS-BRA:2019-08-16</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr"/>
@@ -22872,12 +22872,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>EAS-ROC:27</t>
+          <t>EAS-ROC:2019-08-16</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr"/>
@@ -22930,12 +22930,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>EAS-RUS:28</t>
+          <t>EAS-RUS:2019-08-16</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr"/>
@@ -22988,12 +22988,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>TAY-RES:33</t>
+          <t>TAY-RES:2019-08-16</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr"/>
@@ -23046,12 +23046,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>TAY-TAY:34</t>
+          <t>TAY-TAY:2019-08-16</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr"/>
@@ -23104,12 +23104,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>EAS-ALM:24</t>
+          <t>EAS-ALM:2019-08-17</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr"/>
@@ -23162,12 +23162,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>EAS-PUM:26</t>
+          <t>EAS-PUM:2019-08-17</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
@@ -23220,12 +23220,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>GUN-R32:31</t>
+          <t>GUN-R32:2019-08-17</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr"/>
@@ -23278,12 +23278,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:29</t>
+          <t>GUN-GRJ:2019-08-18</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
@@ -23336,12 +23336,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>GUN-GUN:30</t>
+          <t>GUN-GUN:2019-08-18</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr"/>
@@ -23394,12 +23394,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>GUN-TUN:32</t>
+          <t>GUN-TUN:2019-08-18</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr"/>
@@ -23452,12 +23452,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>CT-BUNN:1</t>
+          <t>CT-BUNN:2019-08-28</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr"/>
@@ -23510,12 +23510,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>CT-NEPA:5</t>
+          <t>CT-NEPA:2019-08-28</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr"/>
@@ -23568,12 +23568,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>CT-PHEL:7</t>
+          <t>CT-PHEL:2019-08-28</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr"/>
@@ -23626,12 +23626,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>CT-STIL:10</t>
+          <t>CT-STIL:2019-08-28</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
@@ -23684,12 +23684,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>CT-UNIO:12</t>
+          <t>CT-UNIO:2019-08-28</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr"/>
@@ -23742,12 +23742,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>CT-FARM:3</t>
+          <t>CT-FARM:2019-08-29</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
@@ -23800,12 +23800,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:11</t>
+          <t>CT-THOM:2019-08-29</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr"/>
@@ -23858,12 +23858,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>BLU-BLU:35</t>
+          <t>BLU-BLU:2019-09-04</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
@@ -23916,12 +23916,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>BLU-TID:36</t>
+          <t>BLU-TID:2019-09-04</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr"/>
@@ -23974,12 +23974,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>LOO-BLU:37</t>
+          <t>LOO-BLU:2019-09-04</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
@@ -24032,12 +24032,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS1:38</t>
+          <t>HJA-WS1:2019-09-04</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr"/>
@@ -24090,12 +24090,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS2:39</t>
+          <t>HJA-WS2:2019-09-04</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
@@ -24148,12 +24148,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>MCK-WAL:40</t>
+          <t>MCK-WAL:2019-09-04</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>WIL-HAR:43</t>
+          <t>WIL-HAR:2019-09-04</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
@@ -24264,12 +24264,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>WIL-COR:41</t>
+          <t>WIL-COR:2019-09-06</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr"/>
@@ -24322,12 +24322,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>WIL-GOS:42</t>
+          <t>WIL-GOS:2019-09-06</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr"/>
@@ -24380,12 +24380,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>WIL-JAS:44</t>
+          <t>WIL-JAS:2019-09-06</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr"/>
@@ -24438,12 +24438,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:45</t>
+          <t>WIL-POR:2019-09-07</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
@@ -24496,12 +24496,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>BRO-LAP:15</t>
+          <t>BRO-LAP:2019-09-10</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr"/>
@@ -24554,12 +24554,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>CUL-LAP:16</t>
+          <t>CUL-LAP:2019-09-10</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr"/>
@@ -24612,12 +24612,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>DES-BFA:17</t>
+          <t>DES-BFA:2019-09-10</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr"/>
@@ -24670,12 +24670,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>DES-LAP:18</t>
+          <t>DES-LAP:2019-09-10</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -24728,12 +24728,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>DES-WIC:21</t>
+          <t>DES-WIC:2019-09-10</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr"/>
@@ -24786,12 +24786,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>LDS-LAP:22</t>
+          <t>LDS-LAP:2019-09-10</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -24844,12 +24844,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>DES-MAD:19</t>
+          <t>DES-MAD:2019-09-11</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
@@ -24902,12 +24902,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:20</t>
+          <t>DES-MOO:2019-09-11</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:135</t>
+          <t>DES-MOO:2019-10-01</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr"/>
@@ -25018,12 +25018,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:148</t>
+          <t>WIL-POR:2019-10-01</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
@@ -25076,12 +25076,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>EAS-ALM:67</t>
+          <t>EAS-ALM:2019-10-18</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr"/>
@@ -25134,12 +25134,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>GUN-GUN:73</t>
+          <t>GUN-GUN:2019-10-18</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
@@ -25192,12 +25192,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>GUN-R32:74</t>
+          <t>GUN-R32:2019-10-18</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
@@ -25250,12 +25250,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>TAY-RES:76</t>
+          <t>TAY-RES:2019-10-18</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
@@ -25308,12 +25308,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>TAY-TAY:77</t>
+          <t>TAY-TAY:2019-10-18</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr"/>
@@ -25366,12 +25366,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>EAS-BRA:68</t>
+          <t>EAS-BRA:2019-10-19</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
@@ -25424,12 +25424,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>EAS-PUM:69</t>
+          <t>EAS-PUM:2019-10-19</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -25482,12 +25482,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>EAS-ROC:70</t>
+          <t>EAS-ROC:2019-10-19</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -25540,12 +25540,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>EAS-RUS:71</t>
+          <t>EAS-RUS:2019-10-19</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -25598,12 +25598,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:72</t>
+          <t>GUN-GRJ:2019-10-20</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
@@ -25656,12 +25656,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>GUN-TUN:75</t>
+          <t>GUN-TUN:2019-10-20</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr"/>
@@ -25714,12 +25714,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>CT-EBRA:47</t>
+          <t>CT-EBRA:2019-11-04</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
@@ -25772,12 +25772,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>CT-MOOS:49</t>
+          <t>CT-MOOS:2019-11-04</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
@@ -25830,12 +25830,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>CT-PASS:51</t>
+          <t>CT-PASS:2019-11-04</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
@@ -25888,12 +25888,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>CT-SLPR:54</t>
+          <t>CT-SLPR:2019-11-04</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
@@ -25946,12 +25946,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>CT-POPE:53</t>
+          <t>CT-POPE:2019-11-05</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
@@ -26004,12 +26004,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>CT-W9:58</t>
+          <t>CT-W9:2019-11-05</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
@@ -26062,12 +26062,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>CT-FARM:48</t>
+          <t>CT-FARM:2019-11-07</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -26120,12 +26120,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>CT-STIL:55</t>
+          <t>CT-STIL:2019-11-07</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
@@ -26178,12 +26178,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:56</t>
+          <t>CT-THOM:2019-11-07</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
@@ -26236,12 +26236,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>CT-UNIO:57</t>
+          <t>CT-UNIO:2019-11-07</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
@@ -26294,12 +26294,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>CT-BUNN:46</t>
+          <t>CT-BUNN:2019-11-08</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
@@ -26352,12 +26352,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>CT-NEPA:50</t>
+          <t>CT-NEPA:2019-11-08</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
@@ -26410,12 +26410,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>CT-PHEL:52</t>
+          <t>CT-PHEL:2019-11-08</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
@@ -26468,12 +26468,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:136</t>
+          <t>DES-MOO:2019-11-10</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
@@ -26526,12 +26526,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:149</t>
+          <t>WIL-POR:2019-11-10</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
@@ -26584,12 +26584,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>BRO-LAP:59</t>
+          <t>BRO-LAP:2019-11-20</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr"/>
@@ -26642,12 +26642,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>CUL-LAP:60</t>
+          <t>CUL-LAP:2019-11-20</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
@@ -26700,12 +26700,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>DES-LAP:62</t>
+          <t>DES-LAP:2019-11-20</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr"/>
@@ -26758,12 +26758,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>DES-WIC:65</t>
+          <t>DES-WIC:2019-11-20</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
@@ -26816,12 +26816,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>LDS-LAP:82</t>
+          <t>LDS-LAP:2019-11-20</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr"/>
@@ -26874,12 +26874,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>DES-BFA:61</t>
+          <t>DES-BFA:2019-11-21</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr"/>
@@ -26932,12 +26932,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>DES-MAD:63</t>
+          <t>DES-MAD:2019-11-21</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
@@ -26990,12 +26990,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:64</t>
+          <t>DES-MOO:2019-11-21</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
@@ -27048,12 +27048,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>WHY-SIS:66</t>
+          <t>WHY-SIS:2019-11-21</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
@@ -27106,12 +27106,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>TRO-GAT:85</t>
+          <t>TRO-GAT:2019-11-21</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr"/>
@@ -27164,12 +27164,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:142</t>
+          <t>GUN-GRJ:2019-11-24</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
@@ -27222,12 +27222,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:132</t>
+          <t>CT-THOM:2019-12-03</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr"/>
@@ -27280,12 +27280,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>MCK-WAL:84</t>
+          <t>MCK-WAL:2019-12-05</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr"/>
@@ -27338,12 +27338,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>WIL-GOS:87</t>
+          <t>WIL-GOS:2019-12-05</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr"/>
@@ -27396,12 +27396,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>WIL-HAR:88</t>
+          <t>WIL-HAR:2019-12-05</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr"/>
@@ -27454,12 +27454,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>WIL-JAS:89</t>
+          <t>WIL-JAS:2019-12-05</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr"/>
@@ -27512,12 +27512,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>WIL-COR:86</t>
+          <t>WIL-COR:2019-12-06</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr"/>
@@ -27570,12 +27570,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:90</t>
+          <t>WIL-POR:2019-12-08</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
@@ -27628,12 +27628,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>BLU-BLU:78</t>
+          <t>BLU-BLU:2019-12-10</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr"/>
@@ -27686,12 +27686,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>BLU-TID:79</t>
+          <t>BLU-TID:2019-12-10</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr"/>
@@ -27744,12 +27744,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS1:80</t>
+          <t>HJA-WS1:2019-12-10</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr"/>
@@ -27802,12 +27802,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS2:81</t>
+          <t>HJA-WS2:2019-12-10</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr"/>
@@ -27860,12 +27860,12 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>LOO-BLU:83</t>
+          <t>LOO-BLU:2019-12-10</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr"/>
@@ -27918,12 +27918,12 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:137</t>
+          <t>DES-MOO:2019-12-27</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
@@ -27976,12 +27976,12 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:143</t>
+          <t>GUN-GRJ:2020-01-08</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
@@ -28034,12 +28034,12 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>BLU-BLU:120</t>
+          <t>BLU-BLU:2020-01-23</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr"/>
@@ -28092,12 +28092,12 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>BLU-TID:121</t>
+          <t>BLU-TID:2020-01-23</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS1:122</t>
+          <t>HJA-WS1:2020-01-23</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr"/>
@@ -28208,12 +28208,12 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS2:123</t>
+          <t>HJA-WS2:2020-01-23</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr"/>
@@ -28266,12 +28266,12 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>LOO-BLU:124</t>
+          <t>LOO-BLU:2020-01-23</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr"/>
@@ -28324,12 +28324,12 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>MCK-WAL:125</t>
+          <t>MCK-WAL:2020-01-23</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr"/>
@@ -28382,12 +28382,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>WIL-COR:127</t>
+          <t>WIL-COR:2020-01-24</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr"/>
@@ -28440,12 +28440,12 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>WIL-HAR:129</t>
+          <t>WIL-HAR:2020-01-24</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr"/>
@@ -28498,12 +28498,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:133</t>
+          <t>CT-THOM:2020-01-24</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr"/>
@@ -28556,12 +28556,12 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:131</t>
+          <t>WIL-POR:2020-01-26</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr"/>
@@ -28614,12 +28614,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:144</t>
+          <t>GUN-GRJ:2020-01-29</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr"/>
@@ -28672,12 +28672,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>DES-MAD:108</t>
+          <t>DES-MAD:2020-02-04</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
@@ -28730,12 +28730,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>DES-WIC:110</t>
+          <t>DES-WIC:2020-02-04</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr"/>
@@ -28788,12 +28788,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>LDS-LAP:111</t>
+          <t>LDS-LAP:2020-02-04</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr"/>
@@ -28846,12 +28846,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>WHY-SIS:112</t>
+          <t>WHY-SIS:2020-02-04</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr"/>
@@ -28904,12 +28904,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>TRO-GAT:126</t>
+          <t>TRO-GAT:2020-02-04</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr"/>
@@ -28962,12 +28962,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>BRO-LAP:104</t>
+          <t>BRO-LAP:2020-02-05</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr"/>
@@ -29020,12 +29020,12 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>CUL-LAP:105</t>
+          <t>CUL-LAP:2020-02-05</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr"/>
@@ -29078,12 +29078,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>DES-BFA:106</t>
+          <t>DES-BFA:2020-02-05</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr"/>
@@ -29136,12 +29136,12 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>DES-LAP:107</t>
+          <t>DES-LAP:2020-02-05</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr"/>
@@ -29194,12 +29194,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:109</t>
+          <t>DES-MOO:2020-02-08</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
@@ -29252,12 +29252,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>EAS-ALM:113</t>
+          <t>EAS-ALM:2020-02-14</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr"/>
@@ -29310,12 +29310,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>GUN-GUN:117</t>
+          <t>GUN-GUN:2020-02-14</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr"/>
@@ -29368,12 +29368,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>GUN-R32:118</t>
+          <t>GUN-R32:2020-02-14</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr"/>
@@ -29426,12 +29426,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>EAS-PUM:114</t>
+          <t>EAS-PUM:2020-02-15</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr"/>
@@ -29484,12 +29484,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>TAY-RES:119</t>
+          <t>TAY-RES:2020-02-15</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
@@ -29542,12 +29542,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>EAS-ROC:115</t>
+          <t>EAS-ROC:2020-02-20</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr"/>
@@ -29600,12 +29600,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>EAS-RUS:116</t>
+          <t>EAS-RUS:2020-02-20</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr"/>
@@ -29658,12 +29658,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:134</t>
+          <t>CT-THOM:2020-03-02</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr"/>
@@ -29716,12 +29716,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:138</t>
+          <t>DES-MOO:2020-03-08</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr"/>
@@ -29774,12 +29774,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:151</t>
+          <t>WIL-POR:2020-03-08</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr"/>
@@ -29832,12 +29832,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:145</t>
+          <t>GUN-GRJ:2020-03-10</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr"/>
@@ -29890,12 +29890,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>CT-MOOS:94</t>
+          <t>CT-MOOS:2020-03-12</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr"/>
@@ -29948,12 +29948,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>CT-SLPR:99</t>
+          <t>CT-SLPR:2020-03-12</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr"/>
@@ -30006,12 +30006,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>CT-EBRA:92</t>
+          <t>CT-EBRA:2020-03-13</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr"/>
@@ -30064,12 +30064,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>CT-PASS:96</t>
+          <t>CT-PASS:2020-03-13</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr"/>
@@ -30122,12 +30122,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>CT-POPE:98</t>
+          <t>CT-POPE:2020-03-13</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr"/>
@@ -30180,12 +30180,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>CT-W9:103</t>
+          <t>CT-W9:2020-03-13</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr"/>
@@ -30238,12 +30238,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:139</t>
+          <t>DES-MOO:2020-04-03</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr"/>
@@ -30296,12 +30296,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:152</t>
+          <t>WIL-POR:2020-04-03</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr"/>
@@ -30354,12 +30354,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>BLU-BLU:170</t>
+          <t>BLU-BLU:2020-04-21</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr"/>
@@ -30412,12 +30412,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>BLU-TID:171</t>
+          <t>BLU-TID:2020-04-21</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr"/>
@@ -30470,12 +30470,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS1:172</t>
+          <t>HJA-WS1:2020-04-21</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr"/>
@@ -30528,12 +30528,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>HJA-WS2:173</t>
+          <t>HJA-WS2:2020-04-21</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr"/>
@@ -30586,12 +30586,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>LOO-BLU:174</t>
+          <t>LOO-BLU:2020-04-21</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr"/>
@@ -30644,12 +30644,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>MCK-WAL:175</t>
+          <t>MCK-WAL:2020-04-23</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr"/>
@@ -30702,12 +30702,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>WIL-COR:176</t>
+          <t>WIL-COR:2020-04-23</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr"/>
@@ -30760,12 +30760,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>WIL-GOS:177</t>
+          <t>WIL-GOS:2020-04-23</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr"/>
@@ -30818,12 +30818,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>WIL-HAR:178</t>
+          <t>WIL-HAR:2020-04-23</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr"/>
@@ -30876,12 +30876,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>WIL-JAS:179</t>
+          <t>WIL-JAS:2020-04-23</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr"/>
@@ -30934,12 +30934,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:146</t>
+          <t>GUN-GRJ:2020-04-24</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr"/>
@@ -30992,12 +30992,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:180</t>
+          <t>WIL-POR:2020-04-27</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr"/>
@@ -31050,12 +31050,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>BRO-LAP:181</t>
+          <t>BRO-LAP:2020-05-07</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr"/>
@@ -31108,12 +31108,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>CUL-LAP:182</t>
+          <t>CUL-LAP:2020-05-07</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr"/>
@@ -31166,12 +31166,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>DES-BFA:183</t>
+          <t>DES-BFA:2020-05-07</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr"/>
@@ -31224,12 +31224,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>DES-LAP:184</t>
+          <t>DES-LAP:2020-05-07</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr"/>
@@ -31282,12 +31282,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>DES-MAD:185</t>
+          <t>DES-MAD:2020-05-07</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr"/>
@@ -31340,12 +31340,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>DES-WIC:187</t>
+          <t>DES-WIC:2020-05-07</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr"/>
@@ -31398,12 +31398,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>LDS-LAP:188</t>
+          <t>LDS-LAP:2020-05-07</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr"/>
@@ -31456,12 +31456,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>WHY-SIS:189</t>
+          <t>WHY-SIS:2020-05-07</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr"/>
@@ -31514,12 +31514,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>TRO-GAT:190</t>
+          <t>TRO-GAT:2020-05-07</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr"/>
@@ -31572,12 +31572,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:186</t>
+          <t>DES-MOO:2020-05-13</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr"/>
@@ -31630,12 +31630,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>CT-EBRA:154</t>
+          <t>CT-EBRA:2020-06-05</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr"/>
@@ -31688,12 +31688,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>CT-MOOS:155</t>
+          <t>CT-MOOS:2020-06-05</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr"/>
@@ -31746,12 +31746,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>CT-PASS:156</t>
+          <t>CT-PASS:2020-06-05</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr"/>
@@ -31804,12 +31804,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>CT-POPE:157</t>
+          <t>CT-POPE:2020-06-05</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr"/>
@@ -31862,12 +31862,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>CT-SLPR:158</t>
+          <t>CT-SLPR:2020-06-05</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr"/>
@@ -31920,12 +31920,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>CT-BUNN:160</t>
+          <t>CT-BUNN:2020-06-05</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr"/>
@@ -31978,12 +31978,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>CT-PHEL:163</t>
+          <t>CT-PHEL:2020-06-05</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr"/>
@@ -32036,12 +32036,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>CT-UNIO:166</t>
+          <t>CT-UNIO:2020-06-05</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr"/>
@@ -32094,12 +32094,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>CT-W9:159</t>
+          <t>CT-W9:2020-06-06</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr"/>
@@ -32152,12 +32152,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>CT-FARM:161</t>
+          <t>CT-FARM:2020-06-06</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr"/>
@@ -32210,12 +32210,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>CT-NEPA:162</t>
+          <t>CT-NEPA:2020-06-06</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr"/>
@@ -32268,12 +32268,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>CT-STIL:164</t>
+          <t>CT-STIL:2020-06-06</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr"/>
@@ -32326,12 +32326,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:165</t>
+          <t>CT-THOM:2020-06-06</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr"/>
@@ -32384,12 +32384,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:140</t>
+          <t>DES-MOO:2020-06-21</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr"/>
@@ -32442,12 +32442,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:228</t>
+          <t>WIL-POR:2020-06-21</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr"/>
@@ -32500,12 +32500,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:147</t>
+          <t>GUN-GRJ:2020-06-23</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr"/>
@@ -32558,12 +32558,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:224</t>
+          <t>DES-MOO:2020-07-30</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr"/>
@@ -32616,12 +32616,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:229</t>
+          <t>WIL-POR:2020-07-30</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr"/>
@@ -32674,12 +32674,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>GUN-GRJ:169</t>
+          <t>GUN-GRJ:2020-08-05</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr"/>
@@ -32732,12 +32732,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:167</t>
+          <t>CT-THOM:2020-08-30</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr"/>
@@ -32790,12 +32790,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>DES-MOO:225</t>
+          <t>DES-MOO:2020-09-03</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr"/>
@@ -32848,12 +32848,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>WIL-POR:230</t>
+          <t>WIL-POR:2020-09-03</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr"/>
@@ -32906,12 +32906,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>CT-THOM:168</t>
+          <t>CT-THOM:2020-10-01</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Site:wrol_sample_id</t>
+          <t>Site:date</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr"/>
